--- a/monitor_xlsx/20260203.xlsx
+++ b/monitor_xlsx/20260203.xlsx
@@ -1176,7 +1176,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2659,6 +2659,112 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>936</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1768</v>
+      </c>
+      <c r="F22" s="22" t="n">
+        <v>-366</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1281</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1312</v>
+      </c>
+      <c r="J22" t="n">
+        <v>83</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2425</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12136</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-47601</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1185</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5512</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G23" t="n">
+        <v>120</v>
+      </c>
+      <c r="H23" t="n">
+        <v>236</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-662</v>
+      </c>
+      <c r="J23" t="n">
+        <v>97</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2626</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13278</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-140175</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260203.xlsx
+++ b/monitor_xlsx/20260203.xlsx
@@ -1176,7 +1176,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2765,6 +2765,165 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>962</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>826</v>
+      </c>
+      <c r="F24" s="22" t="n">
+        <v>-77</v>
+      </c>
+      <c r="G24" t="n">
+        <v>177</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-158</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>624</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>-85</v>
+      </c>
+      <c r="G25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-45</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-17</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3193</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-99</v>
+      </c>
+      <c r="H26" t="n">
+        <v>161</v>
+      </c>
+      <c r="I26" t="n">
+        <v>290</v>
+      </c>
+      <c r="J26" t="n">
+        <v>56</v>
+      </c>
+      <c r="K26" t="n">
+        <v>924</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4564</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-106274</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260203.xlsx
+++ b/monitor_xlsx/20260203.xlsx
@@ -1176,7 +1176,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2924,6 +2924,59 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7797</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>-1005</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-816</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-89</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-175</v>
+      </c>
+      <c r="J27" t="n">
+        <v>290</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6307</v>
+      </c>
+      <c r="L27" t="n">
+        <v>32312</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-58944</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
